--- a/analysis/outputs/animal_disease_RESULTS_2006_2025.xlsx
+++ b/analysis/outputs/animal_disease_RESULTS_2006_2025.xlsx
@@ -42,6 +42,10 @@
     <sheet name="Audit_2026_Exclusion" sheetId="33" state="visible" r:id="rId33"/>
     <sheet name="Audit_2005_Exclusion" sheetId="34" state="visible" r:id="rId34"/>
     <sheet name="QC_Geography_Unharmonised" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="Geo_Recoding_Audit" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="Geo_QA_Division_Review" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="QC_Geo_Cleaning_Reconciliation" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="QGIS_State_Dataset" sheetId="39" state="visible" r:id="rId39"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2449,7 +2453,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nigeria (division not specified)</t>
+          <t>Nigeria (state not specified)</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -7392,7 +7396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7789,7 +7793,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>18. State x disease matrix reconciles to geographic totals</t>
+          <t>21. Geographic administrative-division cleaning completed</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -7799,14 +7803,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>38 administrative divisions; column sums equal national totals for all 3 diseases</t>
+          <t>State_Clean derived from 'Administrative Division'; raw column preserved unchanged. Actions: Unchanged (already a state-level value)=1095; Flagged (non-state entity, not recoded)=6; Rename (spelling correction)=6; Recode (LGA -&gt; parent state)=5. 7 mapped values audited in Geo_Recoding_Audit</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10. 2012 Rabies annual totals reproduced</t>
+          <t>22. Nassarawa spelling correction verified</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -7816,14 +7820,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>28 raw records; outbreaks=19 cases=1667 deaths=93 killed=134 slaughtered=4</t>
+          <t>6 rows renamed Nassarawa -&gt; Nasarawa (years 2021-2022); 0 rows retain the misspelling in State_Clean; 'Nasarawa' present in the cleaned geography, 'Nassarawa' absent</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10b. Largest single 2012 Rabies record verified (Bauchi, Jul-Dec, domestic dogs)</t>
+          <t>23. Batagarawa -&gt; Katsina verified</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -7833,14 +7837,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1575 cases = 94.48% of 2012 Rabies cases; no field in the quantitative dataset identifies a cause</t>
+          <t>1 raw row(s) reassigned to Katsina, all in year(s) 2026; 0 of them fall inside the 2006-2025 study period, so the study-period geography is unchanged by this recoding. 'Batagarawa' no longer appears as a division in the cleaned study dataset</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>11. HPAI 2009-2013 reporting gap confirmed in raw data</t>
+          <t>24. Gwale -&gt; Kano verified</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7850,14 +7854,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0 HPAI raw rows across 2009-2013; other diseases reported in the same years (Rabies 93 rows, Trypanosomosis 30 rows), so the gap is disease-specific, not a whole-country reporting outage. Retained as NA, not zero</t>
+          <t>1 raw row(s) reassigned to Kano, all in year(s) 2026; 0 of them fall inside the 2006-2025 study period, so the study-period geography is unchanged by this recoding. 'Gwale' no longer appears as a division in the cleaned study dataset</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>12. 2024 independently verified from raw data</t>
+          <t>25. Jos North -&gt; Plateau verified</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7867,14 +7871,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>HPAI 5 outbreaks/4,156 cases; Rabies 184 outbreaks/190 cases; Trypanosomosis no observations</t>
+          <t>1 raw row(s) reassigned to Plateau, all in year(s) 2026; 0 of them fall inside the 2006-2025 study period, so the study-period geography is unchanged by this recoding. 'Jos North' no longer appears as a division in the cleaned study dataset</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>13. 2025 independently verified from raw data</t>
+          <t>26. Toro -&gt; Bauchi verified</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7884,14 +7888,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>HPAI 36 outbreaks/117,032 cases; Rabies 125 outbreaks/125 cases; Trypanosomosis no observations</t>
+          <t>1 raw row(s) reassigned to Bauchi, all in year(s) 2026; 0 of them fall inside the 2006-2025 study period, so the study-period geography is unchanged by this recoding. 'Toro' no longer appears as a division in the cleaned study dataset</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>14. 2026 exclusion audited and justified</t>
+          <t>27. Ungogo -&gt; Kano verified</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7901,14 +7905,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>6 rows, HPAI only, Jan-Jun 2026 only: 9 outbreaks, 27,127 cases, 9,008 deaths, 18,189 killed/disposed, 0 slaughtered; divisions Batagarawa, Bauchi, Gwale, Jos North, Toro, Ungogo (LGA-level, unlike the state-level 2006-2025 records)</t>
+          <t>1 raw row(s) reassigned to Kano, all in year(s) 2026; 0 of them fall inside the 2006-2025 study period, so the study-period geography is unchanged by this recoding. 'Ungogo' no longer appears as a division in the cleaned study dataset</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>17b. Cutoff sensitivity totals match specification for all 3 windows</t>
+          <t>28. Geographic recoding did not alter national disease totals</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -7918,22 +7922,192 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>45 metric-disease-period cells verified across 2006-2023 / 2006-2024 / 2006-2025</t>
+          <t>HPAI: 1273 -&gt; 1273 (diff 0); Rabies: 1232 -&gt; 1232 (diff 0); Trypanosomosis: 130 -&gt; 130 (diff 0); ALL THREE: 2635 -&gt; 2635 (diff 0)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>29. State-level totals reconcile before vs after geographic cleaning</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Cleaning is a relabelling only: 6 study-period rows changed state label (all 6 Nassarawa-&gt;Nasarawa; the 5 LGA rows are 2026-only and outside the study period). Division count 38 -&gt; 38; national totals per disease and overall unchanged; cleaned geography still reconciles to the annual tables</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>30. QGIS-ready state dataset uses standardized state names</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>37 rows = Nigeria's 36 states + FCT, names matching standard shapefile spellings; 0 unrecognised values. 1 value(s) flagged for review and held OUT of the state file: 'Nigeria' (6 rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>18. State x disease matrix reconciles to geographic totals</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>38 administrative divisions; column sums equal national totals for all 3 diseases</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>10. 2012 Rabies annual totals reproduced</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>28 raw records; outbreaks=19 cases=1667 deaths=93 killed=134 slaughtered=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>10b. Largest single 2012 Rabies record verified (Bauchi, Jul-Dec, domestic dogs)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1575 cases = 94.48% of 2012 Rabies cases; no field in the quantitative dataset identifies a cause</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>11. HPAI 2009-2013 reporting gap confirmed in raw data</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0 HPAI raw rows across 2009-2013; other diseases reported in the same years (Rabies 93 rows, Trypanosomosis 30 rows), so the gap is disease-specific, not a whole-country reporting outage. Retained as NA, not zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>12. 2024 independently verified from raw data</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>HPAI 5 outbreaks/4,156 cases; Rabies 184 outbreaks/190 cases; Trypanosomosis no observations</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>13. 2025 independently verified from raw data</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>HPAI 36 outbreaks/117,032 cases; Rabies 125 outbreaks/125 cases; Trypanosomosis no observations</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>14. 2026 exclusion audited and justified</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>6 rows, HPAI only, Jan-Jun 2026 only: 9 outbreaks, 27,127 cases, 9,008 deaths, 18,189 killed/disposed, 0 slaughtered; divisions Batagarawa, Bauchi, Gwale, Jos North, Toro, Ungogo (LGA-level, unlike the state-level 2006-2025 records)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>17b. Cutoff sensitivity totals match specification for all 3 windows</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>45 metric-disease-period cells verified across 2006-2023 / 2006-2024 / 2006-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>17. Figure datasets reconcile to tables</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Figure_1_Data==Table 2, Figure_2_Data==Table 3, Figure_3_Data==Table 4, Figure_4_Data==Table 5 (cell-for-cell, NA preserved)</t>
         </is>
@@ -10579,7 +10753,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Nigeria (division not specified)</t>
+          <t>Nigeria (state not specified)</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -10671,7 +10845,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Nigeria (division not specified), Rivers</t>
+          <t>Nigeria (state not specified), Rivers</t>
         </is>
       </c>
     </row>
@@ -12563,7 +12737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12615,7 +12789,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Administrative divisions</t>
+          <t>Administrative divisions (as in raw file)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -12627,60 +12801,84 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Reported outbreaks</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>9</v>
+          <t>Administrative level of those values</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>5 of the 6 are LGAs, not states (Batagarawa, Gwale, Jos North, Toro, Ungogo); only Bauchi is a state. The 2006-2025 records are all state-level, so 2026 is reported at a different administrative granularity from the study period.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Reported cases</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>27127</v>
+          <t>Parent states after cleaning (State_Clean)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bauchi, Kano, Katsina, Plateau</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Deaths</t>
+          <t>Reported outbreaks</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9008</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Killed and disposed of</t>
+          <t>Reported cases</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18189</v>
+        <v>27127</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Slaughtered</t>
+          <t>Deaths</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>9008</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Killed and disposed of</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>18189</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Slaughtered</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Exclusion rationale</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Only January-June 2026 observations are available; no July-December 2026 observations are present, so 2026 is not a complete calendar year in this extract</t>
         </is>
@@ -13377,6 +13575,3476 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Original_value</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Cleaned_state</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Rows_affected</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Years_affected</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Rows_in_2006_2025_study_period</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Nassarawa</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Nasarawa</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Rename</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Spelling correction; same Nigerian state</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2021, 2022</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Batagarawa</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Recode</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>LGA -&gt; parent state</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gwale</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Recode</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>LGA -&gt; parent state</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Jos North</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Recode</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>LGA -&gt; parent state</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Toro</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Bauchi</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Recode</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>LGA -&gt; parent state</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Ungogo</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Recode</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>LGA -&gt; parent state</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Nigeria (state not specified)</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Flag only</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>National-level record with no state resolved; retained as a separate non-mappable row</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2005, 2014</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Raw_value</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>State_Clean</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Rows</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Abia</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Abia</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Recognised Nigerian state / FCT, matches shapefile naming</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Recognised Nigerian state / FCT, matches shapefile naming</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Akwa Ibom</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Akwa Ibom</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Recognised Nigerian state / FCT, matches shapefile naming</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Anambra</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Anambra</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>24</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Recognised Nigerian state / FCT, matches shapefile naming</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Batagarawa</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>LGA recoded to parent state</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Bauchi</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bauchi</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>87</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Recognised Nigerian state / FCT, matches shapefile naming</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Bayelsa</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Bayelsa</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>20</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Recognised Nigerian state / FCT, matches shapefile naming</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>28</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Recognised Nigerian state / FCT, matches shapefile naming</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>14</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Recognised Nigerian state / FCT, matches shapefile naming</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Cross River</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Cross River</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Recognised Nigerian state / FCT, matches shapefile naming</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>33</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Recognised Nigerian state / FCT, matches shapefile naming</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Ebonyi</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ebonyi</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>19</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Recognised Nigerian state / FCT, matches shapefile naming</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Edo</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Edo</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>24</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Recognised Nigerian state / FCT, matches shapefile naming</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ekiti</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ekiti</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>20</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Recognised Nigerian state / FCT, matches shapefile naming</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Enugu</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Enugu</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Recognised Nigerian state / FCT, matches shapefile naming</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Federal Capital Territory</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Federal Capital Territory</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>40</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Recognised Nigerian state / FCT, matches shapefile naming</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Gombe</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Gombe</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>50</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Recognised Nigerian state / FCT, matches shapefile naming</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Gwale</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>LGA recoded to parent state</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Imo</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Imo</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>12</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Recognised Nigerian state / FCT, matches shapefile naming</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Jigawa</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Jigawa</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>26</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Recognised Nigerian state / FCT, matches shapefile naming</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Jos North</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>LGA recoded to parent state</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>71</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Recognised Nigerian state / FCT, matches shapefile naming</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>79</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Recognised Nigerian state / FCT, matches shapefile naming</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>26</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Recognised Nigerian state / FCT, matches shapefile naming</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>28</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Recognised Nigerian state / FCT, matches shapefile naming</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Kogi</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kogi</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>12</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Recognised Nigerian state / FCT, matches shapefile naming</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Kwara</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Kwara</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>25</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Recognised Nigerian state / FCT, matches shapefile naming</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>30</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Recognised Nigerian state / FCT, matches shapefile naming</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Nasarawa</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Nasarawa</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>22</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Recognised Nigerian state / FCT, matches shapefile naming</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Nassarawa</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nasarawa</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>6</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Spelling corrected</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Niger</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Niger</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>45</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Recognised Nigerian state / FCT, matches shapefile naming</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Nigeria (state not specified)</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>6</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>FLAGGED FOR REVIEW</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Not a state or LGA: national-level record with no state resolved. Not recoded - excluded from state-level maps and reported separately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Ogun</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Ogun</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>32</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Recognised Nigerian state / FCT, matches shapefile naming</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Ondo</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Ondo</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>14</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Recognised Nigerian state / FCT, matches shapefile naming</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Osun</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Osun</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>32</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Recognised Nigerian state / FCT, matches shapefile naming</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>26</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Recognised Nigerian state / FCT, matches shapefile naming</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>96</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Recognised Nigerian state / FCT, matches shapefile naming</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>16</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Recognised Nigerian state / FCT, matches shapefile naming</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>13</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Recognised Nigerian state / FCT, matches shapefile naming</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Taraba</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Taraba</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>20</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Recognised Nigerian state / FCT, matches shapefile naming</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Toro</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Bauchi</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>LGA recoded to parent state</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Ungogo</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>LGA recoded to parent state</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>14</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Recognised Nigerian state / FCT, matches shapefile naming</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>24</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Recognised Nigerian state / FCT, matches shapefile naming</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Disease</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Before_cleaning</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>After_cleaning</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HPAI</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1273</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1273</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1232</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1232</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Trypanosomosis</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>130</v>
+      </c>
+      <c r="C4" t="n">
+        <v>130</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ALL THREE</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2635</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2635</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>HPAI_outbreaks</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>HPAI_outbreaks_map0</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>HPAI_status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Rabies_outbreaks</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Rabies_outbreaks_map0</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Rabies_status</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Trypanosomosis_outbreaks</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Trypanosomosis_outbreaks_map0</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Trypanosomosis_status</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Total_reported_outbreaks</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>N_diseases_with_reported_outbreaks</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Missing_value_treatment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Abia</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>No reported outbreaks in extracted dataset (not an observed zero)</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Blank in *_outbreaks means no WAHIS observation; the *_map0 column 0-fills it for join convenience only and must not be read as zero burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>22</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Blank in *_outbreaks means no WAHIS observation; the *_map0 column 0-fills it for join convenience only and must not be read as zero burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Akwa Ibom</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>No reported outbreaks in extracted dataset (not an observed zero)</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>16</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Blank in *_outbreaks means no WAHIS observation; the *_map0 column 0-fills it for join convenience only and must not be read as zero burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Anambra</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C5" t="n">
+        <v>11</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>17</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Blank in *_outbreaks means no WAHIS observation; the *_map0 column 0-fills it for join convenience only and must not be read as zero burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Bauchi</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>60</v>
+      </c>
+      <c r="C6" t="n">
+        <v>60</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>116</v>
+      </c>
+      <c r="F6" t="n">
+        <v>116</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>181</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Blank in *_outbreaks means no WAHIS observation; the *_map0 column 0-fills it for join convenience only and must not be read as zero burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Bayelsa</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>No reported outbreaks in extracted dataset (not an observed zero)</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>16</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Blank in *_outbreaks means no WAHIS observation; the *_map0 column 0-fills it for join convenience only and must not be read as zero burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>23</v>
+      </c>
+      <c r="F8" t="n">
+        <v>23</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>No reported outbreaks in extracted dataset (not an observed zero)</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>25</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Blank in *_outbreaks means no WAHIS observation; the *_map0 column 0-fills it for join convenience only and must not be read as zero burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>No reported outbreaks in extracted dataset (not an observed zero)</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>11</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Blank in *_outbreaks means no WAHIS observation; the *_map0 column 0-fills it for join convenience only and must not be read as zero burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Cross River</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>No reported outbreaks in extracted dataset (not an observed zero)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>19</v>
+      </c>
+      <c r="F10" t="n">
+        <v>19</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>No reported outbreaks in extracted dataset (not an observed zero)</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>19</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Blank in *_outbreaks means no WAHIS observation; the *_map0 column 0-fills it for join convenience only and must not be read as zero burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>42</v>
+      </c>
+      <c r="C11" t="n">
+        <v>42</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>12</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>No reported outbreaks in extracted dataset (not an observed zero)</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>54</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Blank in *_outbreaks means no WAHIS observation; the *_map0 column 0-fills it for join convenience only and must not be read as zero burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ebonyi</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" t="n">
+        <v>12</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>No reported outbreaks in extracted dataset (not an observed zero)</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>15</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Blank in *_outbreaks means no WAHIS observation; the *_map0 column 0-fills it for join convenience only and must not be read as zero burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Edo</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>25</v>
+      </c>
+      <c r="C13" t="n">
+        <v>25</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>No reported outbreaks in extracted dataset (not an observed zero)</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>27</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Blank in *_outbreaks means no WAHIS observation; the *_map0 column 0-fills it for join convenience only and must not be read as zero burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ekiti</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>11</v>
+      </c>
+      <c r="F14" t="n">
+        <v>11</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>No reported outbreaks in extracted dataset (not an observed zero)</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>13</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Blank in *_outbreaks means no WAHIS observation; the *_map0 column 0-fills it for join convenience only and must not be read as zero burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Enugu</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>9</v>
+      </c>
+      <c r="C15" t="n">
+        <v>9</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>7</v>
+      </c>
+      <c r="I15" t="n">
+        <v>7</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>17</v>
+      </c>
+      <c r="L15" t="n">
+        <v>3</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Blank in *_outbreaks means no WAHIS observation; the *_map0 column 0-fills it for join convenience only and must not be read as zero burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Federal Capital Territory</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>31</v>
+      </c>
+      <c r="C16" t="n">
+        <v>31</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>11</v>
+      </c>
+      <c r="F16" t="n">
+        <v>11</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>10</v>
+      </c>
+      <c r="I16" t="n">
+        <v>10</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>52</v>
+      </c>
+      <c r="L16" t="n">
+        <v>3</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Blank in *_outbreaks means no WAHIS observation; the *_map0 column 0-fills it for join convenience only and must not be read as zero burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Gombe</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C17" t="n">
+        <v>15</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>49</v>
+      </c>
+      <c r="F17" t="n">
+        <v>49</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>66</v>
+      </c>
+      <c r="L17" t="n">
+        <v>3</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Blank in *_outbreaks means no WAHIS observation; the *_map0 column 0-fills it for join convenience only and must not be read as zero burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Imo</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>No reported outbreaks in extracted dataset (not an observed zero)</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>7</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Blank in *_outbreaks means no WAHIS observation; the *_map0 column 0-fills it for join convenience only and must not be read as zero burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Jigawa</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>12</v>
+      </c>
+      <c r="C19" t="n">
+        <v>12</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>11</v>
+      </c>
+      <c r="F19" t="n">
+        <v>11</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>27</v>
+      </c>
+      <c r="L19" t="n">
+        <v>3</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Blank in *_outbreaks means no WAHIS observation; the *_map0 column 0-fills it for join convenience only and must not be read as zero burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>70</v>
+      </c>
+      <c r="C20" t="n">
+        <v>70</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>97</v>
+      </c>
+      <c r="F20" t="n">
+        <v>97</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>No reported outbreaks in extracted dataset (not an observed zero)</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>167</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Blank in *_outbreaks means no WAHIS observation; the *_map0 column 0-fills it for join convenience only and must not be read as zero burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>262</v>
+      </c>
+      <c r="C21" t="n">
+        <v>262</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>83</v>
+      </c>
+      <c r="F21" t="n">
+        <v>83</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>No reported outbreaks in extracted dataset (not an observed zero)</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>345</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Blank in *_outbreaks means no WAHIS observation; the *_map0 column 0-fills it for join convenience only and must not be read as zero burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>45</v>
+      </c>
+      <c r="C22" t="n">
+        <v>45</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>7</v>
+      </c>
+      <c r="F22" t="n">
+        <v>7</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>No reported outbreaks in extracted dataset (not an observed zero)</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>52</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Blank in *_outbreaks means no WAHIS observation; the *_map0 column 0-fills it for join convenience only and must not be read as zero burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>6</v>
+      </c>
+      <c r="C23" t="n">
+        <v>6</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>26</v>
+      </c>
+      <c r="F23" t="n">
+        <v>26</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>No reported outbreaks in extracted dataset (not an observed zero)</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>32</v>
+      </c>
+      <c r="L23" t="n">
+        <v>2</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Blank in *_outbreaks means no WAHIS observation; the *_map0 column 0-fills it for join convenience only and must not be read as zero burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Kogi</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>7</v>
+      </c>
+      <c r="L24" t="n">
+        <v>3</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Blank in *_outbreaks means no WAHIS observation; the *_map0 column 0-fills it for join convenience only and must not be read as zero burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Kwara</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>7</v>
+      </c>
+      <c r="F25" t="n">
+        <v>7</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>18</v>
+      </c>
+      <c r="I25" t="n">
+        <v>18</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>26</v>
+      </c>
+      <c r="L25" t="n">
+        <v>3</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Blank in *_outbreaks means no WAHIS observation; the *_map0 column 0-fills it for join convenience only and must not be read as zero burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>137</v>
+      </c>
+      <c r="C26" t="n">
+        <v>137</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>143</v>
+      </c>
+      <c r="L26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Blank in *_outbreaks means no WAHIS observation; the *_map0 column 0-fills it for join convenience only and must not be read as zero burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Nasarawa</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>22</v>
+      </c>
+      <c r="C27" t="n">
+        <v>22</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>27</v>
+      </c>
+      <c r="L27" t="n">
+        <v>3</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Blank in *_outbreaks means no WAHIS observation; the *_map0 column 0-fills it for join convenience only and must not be read as zero burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Niger</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>11</v>
+      </c>
+      <c r="C28" t="n">
+        <v>11</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>7</v>
+      </c>
+      <c r="F28" t="n">
+        <v>7</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>54</v>
+      </c>
+      <c r="I28" t="n">
+        <v>54</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>72</v>
+      </c>
+      <c r="L28" t="n">
+        <v>3</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Blank in *_outbreaks means no WAHIS observation; the *_map0 column 0-fills it for join convenience only and must not be read as zero burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Ogun</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>45</v>
+      </c>
+      <c r="C29" t="n">
+        <v>45</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6</v>
+      </c>
+      <c r="F29" t="n">
+        <v>6</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>No reported outbreaks in extracted dataset (not an observed zero)</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>51</v>
+      </c>
+      <c r="L29" t="n">
+        <v>2</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Blank in *_outbreaks means no WAHIS observation; the *_map0 column 0-fills it for join convenience only and must not be read as zero burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Ondo</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>No reported outbreaks in extracted dataset (not an observed zero)</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5</v>
+      </c>
+      <c r="F30" t="n">
+        <v>5</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>4</v>
+      </c>
+      <c r="I30" t="n">
+        <v>4</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>9</v>
+      </c>
+      <c r="L30" t="n">
+        <v>2</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Blank in *_outbreaks means no WAHIS observation; the *_map0 column 0-fills it for join convenience only and must not be read as zero burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Osun</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>17</v>
+      </c>
+      <c r="F31" t="n">
+        <v>17</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>20</v>
+      </c>
+      <c r="L31" t="n">
+        <v>3</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Blank in *_outbreaks means no WAHIS observation; the *_map0 column 0-fills it for join convenience only and must not be read as zero burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>18</v>
+      </c>
+      <c r="C32" t="n">
+        <v>18</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6</v>
+      </c>
+      <c r="F32" t="n">
+        <v>6</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>26</v>
+      </c>
+      <c r="L32" t="n">
+        <v>3</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Blank in *_outbreaks means no WAHIS observation; the *_map0 column 0-fills it for join convenience only and must not be read as zero burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>308</v>
+      </c>
+      <c r="C33" t="n">
+        <v>308</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>632</v>
+      </c>
+      <c r="F33" t="n">
+        <v>632</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>942</v>
+      </c>
+      <c r="L33" t="n">
+        <v>3</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Blank in *_outbreaks means no WAHIS observation; the *_map0 column 0-fills it for join convenience only and must not be read as zero burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>56</v>
+      </c>
+      <c r="C34" t="n">
+        <v>56</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>No reported outbreaks in extracted dataset (not an observed zero)</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>No reported outbreaks in extracted dataset (not an observed zero)</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>56</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Blank in *_outbreaks means no WAHIS observation; the *_map0 column 0-fills it for join convenience only and must not be read as zero burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>7</v>
+      </c>
+      <c r="C35" t="n">
+        <v>7</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>3</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>No reported outbreaks in extracted dataset (not an observed zero)</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>10</v>
+      </c>
+      <c r="L35" t="n">
+        <v>2</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Blank in *_outbreaks means no WAHIS observation; the *_map0 column 0-fills it for join convenience only and must not be read as zero burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Taraba</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>23</v>
+      </c>
+      <c r="C36" t="n">
+        <v>23</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6</v>
+      </c>
+      <c r="F36" t="n">
+        <v>6</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>No reported outbreaks in extracted dataset (not an observed zero)</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>29</v>
+      </c>
+      <c r="L36" t="n">
+        <v>2</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Blank in *_outbreaks means no WAHIS observation; the *_map0 column 0-fills it for join convenience only and must not be read as zero burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>3</v>
+      </c>
+      <c r="C37" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>8</v>
+      </c>
+      <c r="F37" t="n">
+        <v>8</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>No reported outbreaks in extracted dataset (not an observed zero)</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>11</v>
+      </c>
+      <c r="L37" t="n">
+        <v>2</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Blank in *_outbreaks means no WAHIS observation; the *_map0 column 0-fills it for join convenience only and must not be read as zero burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>8</v>
+      </c>
+      <c r="C38" t="n">
+        <v>8</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>8</v>
+      </c>
+      <c r="F38" t="n">
+        <v>8</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>2</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Reported outbreaks present</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>18</v>
+      </c>
+      <c r="L38" t="n">
+        <v>3</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Blank in *_outbreaks means no WAHIS observation; the *_map0 column 0-fills it for join convenience only and must not be read as zero burden</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
